--- a/event_registration_forms/015_team_recognition_event_request_form--event_registration_forms.xlsx
+++ b/event_registration_forms/015_team_recognition_event_request_form--event_registration_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -505,69 +505,69 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>team_recognition_event_request_form</t>
+          <t>team_recognition_event_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>team_recognition_event_request_form</t>
+          <t>Event Date</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>team_recognition_event_date</t>
+          <t>team_recognition_event_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>team_recognition_event_date</t>
+          <t>Event Time</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>team_recognition_event_time</t>
+          <t>team_recognition_event_venue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>team_recognition_event_time</t>
+          <t>Event Location (Venue)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue</t>
+          <t>team_recognition_event_venue_address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue</t>
+          <t>Event Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,18 +602,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue_address</t>
+          <t>team_recognition_event_venue_city</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,18 +625,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue_city</t>
+          <t>team_recognition_event_venue_state</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue</t>
+          <t>State/Province</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,18 +648,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue_state</t>
+          <t>team_recognition_event_venue_postal_code</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue</t>
+          <t>Postal Code</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,16 +671,108 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue_postal_code</t>
+          <t>team_recognition_event_requesting_member</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>team_recognition_event_venue</t>
+          <t>Requesting Team Member Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>team_recognition_event_team_name</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Team Name</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>team_recognition_event_recognition_type</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Recognition Type</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>team_recognition_event_description</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brief Description of Event</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>team_recognition_event_additional_notes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Additional Notes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
